--- a/brasus/skills/google-workspace/sheets/BRASUS_COMMERCIAL.xlsx
+++ b/brasus/skills/google-workspace/sheets/BRASUS_COMMERCIAL.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1 - MISSIONS DU JOUR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2 - EXÉCUTION JOURNALIÈRE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3 - MES PERFORMANCES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4 - MON HISTORIQUE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5 - PLAN D'AMÉLIORATION" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,6 +135,7 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
@@ -142,6 +143,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001565C0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0037474F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -164,11 +171,11 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="0037474F"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -283,12 +290,6 @@
         <bgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -350,11 +351,13 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -386,8 +389,9 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -446,7 +450,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -455,7 +459,7 @@
     <xf numFmtId="0" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -464,7 +468,7 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -473,25 +477,25 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1188,18 +1192,19 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>🔒 Colonnes A–E verrouillées — Seules STATUT et COMMENTAIRE sont modifiables</t>
+          <t>🔒 Colonnes A–E verrouillées (BRASUS) — Colonnes STATUT et COMMENTAIRE saisissables (fond jaune)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>⏰ Verrouillage automatique à 18h00 (heure d'Abidjan) — Aucune modification après clôture</t>
+          <t>⏰ Verrouillage automatique à 18h00 (heure d'Abidjan) — Toutes les cellules verrouillées après clôture</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CCC2"/>
   <mergeCells count="6">
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="E2:G2"/>
@@ -1443,11 +1448,12 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>⏰ RAPPEL : Clôture automatique à 18h00 — Verrouillage définitif</t>
+          <t>⏰ RAPPEL : Clôture automatique à 18h00 — Verrouillage définitif de toutes les cellules</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CCC2"/>
   <mergeCells count="19">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A12:C12"/>
@@ -1711,6 +1717,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CCC2"/>
   <mergeCells count="20">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
@@ -1744,7 +1751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1828,12 +1835,12 @@
       </c>
       <c r="B7" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C7" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1860,12 +1867,12 @@
       </c>
       <c r="B8" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C8" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1892,12 +1899,12 @@
       </c>
       <c r="B9" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C9" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1924,12 +1931,12 @@
       </c>
       <c r="B10" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C10" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1956,12 +1963,12 @@
       </c>
       <c r="B11" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C11" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1988,12 +1995,12 @@
       </c>
       <c r="B12" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C12" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2020,12 +2027,12 @@
       </c>
       <c r="B13" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2052,12 +2059,12 @@
       </c>
       <c r="B14" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C14" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -2084,12 +2091,12 @@
       </c>
       <c r="B15" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C15" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2116,12 +2123,12 @@
       </c>
       <c r="B16" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C16" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2148,12 +2155,12 @@
       </c>
       <c r="B17" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C17" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2180,12 +2187,12 @@
       </c>
       <c r="B18" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C18" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -2212,12 +2219,12 @@
       </c>
       <c r="B19" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C19" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2244,12 +2251,12 @@
       </c>
       <c r="B20" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -2276,12 +2283,12 @@
       </c>
       <c r="B21" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="C21" s="49" t="inlineStr">
         <is>
-          <t>{{N}}</t>
+          <t>{{N — Généré BRASUS}}</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2307,12 +2314,21 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>🔒 Feuille en lecture seule — Mise à jour automatique par BRASUS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CCC2"/>
+  <mergeCells count="7">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
@@ -2490,11 +2506,12 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>🔒 Plan généré automatiquement chaque lundi à 07:00 — Lecture seule</t>
+          <t>🔒 Plan généré automatiquement chaque lundi à 07:00 — Lecture seule intégrale</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CCC2"/>
   <mergeCells count="17">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A2:B2"/>
